--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manthan Patel\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2337F239-8E35-AF4C-B6AC-7A5EF72323C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB89C7A-AA33-46FF-A653-AEB5E16C85E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1440,16 +1438,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="46.83203125" style="1" customWidth="1"/>
-    <col min="3" max="5" width="15.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="1"/>
+    <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="46.85546875" style="1" customWidth="1"/>
+    <col min="3" max="5" width="15.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1466,7 +1464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1477,13 +1475,13 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>2723</v>
+        <v>2818</v>
       </c>
       <c r="E2" s="5">
-        <v>23.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23.61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1494,13 +1492,13 @@
         <v>8</v>
       </c>
       <c r="D3" s="5">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="E3" s="5">
-        <v>52.48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>52.45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1511,13 +1509,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>590</v>
+        <v>633</v>
       </c>
       <c r="E4" s="5">
-        <v>83.84</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85.2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1528,13 +1526,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>385</v>
+        <v>410</v>
       </c>
       <c r="E5" s="5">
-        <v>113.42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>113.54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1545,13 +1543,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>523</v>
+        <v>575</v>
       </c>
       <c r="E6" s="5">
-        <v>88.42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>90.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1562,13 +1560,13 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <v>1309</v>
+        <v>1438</v>
       </c>
       <c r="E7" s="5">
-        <v>22.19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22.35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1579,13 +1577,13 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>1703</v>
+        <v>1784</v>
       </c>
       <c r="E8" s="5">
-        <v>28.08</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28.17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1596,13 +1594,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>1984</v>
+        <v>2167</v>
       </c>
       <c r="E9" s="5">
-        <v>27.22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27.58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1613,13 +1611,13 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>478</v>
+        <v>545</v>
       </c>
       <c r="E10" s="5">
-        <v>56.85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56.51</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>11</v>
       </c>
@@ -1630,13 +1628,13 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="E11" s="5">
-        <v>142.65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>144.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>12</v>
       </c>
@@ -1647,13 +1645,13 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <v>574</v>
+        <v>604</v>
       </c>
       <c r="E12" s="5">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>87.34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>13</v>
       </c>
@@ -1664,13 +1662,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>1281</v>
+        <v>1678</v>
       </c>
       <c r="E13" s="5">
-        <v>38.75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>36.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>14</v>
       </c>
@@ -1681,13 +1679,13 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>310</v>
+        <v>338</v>
       </c>
       <c r="E14" s="5">
-        <v>136.30000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>138.19999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>15</v>
       </c>
@@ -1701,10 +1699,10 @@
         <v>516</v>
       </c>
       <c r="E15" s="5">
-        <v>55.03</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55.06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>16</v>
       </c>
@@ -1715,13 +1713,13 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>3022</v>
+        <v>3481</v>
       </c>
       <c r="E16" s="5">
-        <v>9.82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>17</v>
       </c>
@@ -1732,13 +1730,13 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>2539</v>
+        <v>2647</v>
       </c>
       <c r="E17" s="5">
-        <v>20.48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>20.57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>18</v>
       </c>
@@ -1749,13 +1747,13 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>2261</v>
+        <v>2407</v>
       </c>
       <c r="E18" s="5">
-        <v>27.89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28.14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>19</v>
       </c>
@@ -1766,13 +1764,13 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>505</v>
+        <v>554</v>
       </c>
       <c r="E19" s="5">
-        <v>76.77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>79.010000000000005</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>20</v>
       </c>
@@ -1783,13 +1781,13 @@
         <v>41</v>
       </c>
       <c r="D20" s="5">
-        <v>237</v>
+        <v>268</v>
       </c>
       <c r="E20" s="5">
-        <v>184.68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>184.52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>21</v>
       </c>
@@ -1800,13 +1798,13 @@
         <v>43</v>
       </c>
       <c r="D21" s="5">
-        <v>1938</v>
+        <v>2070</v>
       </c>
       <c r="E21" s="5">
-        <v>22.26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>22.29</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>22</v>
       </c>
@@ -1817,13 +1815,13 @@
         <v>45</v>
       </c>
       <c r="D22" s="5">
-        <v>409</v>
+        <v>449</v>
       </c>
       <c r="E22" s="5">
-        <v>85.68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>84.88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>23</v>
       </c>
@@ -1834,13 +1832,13 @@
         <v>47</v>
       </c>
       <c r="D23" s="5">
-        <v>1881</v>
+        <v>2171</v>
       </c>
       <c r="E23" s="5">
-        <v>15.67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>15.84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>24</v>
       </c>
@@ -1851,13 +1849,13 @@
         <v>49</v>
       </c>
       <c r="D24" s="5">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="E24" s="5">
-        <v>265.08999999999997</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>264.75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>25</v>
       </c>
@@ -1868,13 +1866,13 @@
         <v>51</v>
       </c>
       <c r="D25" s="5">
-        <v>3812</v>
+        <v>4082</v>
       </c>
       <c r="E25" s="5">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>11.03</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>26</v>
       </c>
@@ -1885,13 +1883,13 @@
         <v>53</v>
       </c>
       <c r="D26" s="5">
-        <v>868</v>
+        <v>907</v>
       </c>
       <c r="E26" s="5">
-        <v>68.86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>69.48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>27</v>
       </c>
@@ -1902,13 +1900,13 @@
         <v>55</v>
       </c>
       <c r="D27" s="5">
-        <v>2230</v>
+        <v>2352</v>
       </c>
       <c r="E27" s="5">
-        <v>26.1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26.04</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>28</v>
       </c>
@@ -1922,10 +1920,10 @@
         <v>48</v>
       </c>
       <c r="E28" s="5">
-        <v>880.09</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>878.52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>30</v>
       </c>
@@ -1936,13 +1934,13 @@
         <v>59</v>
       </c>
       <c r="D29" s="5">
-        <v>543</v>
+        <v>592</v>
       </c>
       <c r="E29" s="5">
-        <v>86.59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>85.87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>31</v>
       </c>
@@ -1953,13 +1951,13 @@
         <v>60</v>
       </c>
       <c r="D30" s="5">
-        <v>483</v>
+        <v>551</v>
       </c>
       <c r="E30" s="5">
-        <v>10.039999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>10.28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>32</v>
       </c>
@@ -1970,13 +1968,13 @@
         <v>61</v>
       </c>
       <c r="D31" s="5">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="E31" s="5">
-        <v>27.94</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27.96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>33</v>
       </c>
@@ -1987,13 +1985,13 @@
         <v>64</v>
       </c>
       <c r="D32" s="5">
-        <v>192</v>
+        <v>222</v>
       </c>
       <c r="E32" s="5">
-        <v>100.91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>104.77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>34</v>
       </c>
@@ -2004,10 +2002,10 @@
         <v>65</v>
       </c>
       <c r="D33" s="5">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="E33" s="5">
-        <v>132.55000000000001</v>
+        <v>139.36000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manthan Patel\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FB89C7A-AA33-46FF-A653-AEB5E16C85E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2CFAD4-C68E-6F45-8C4C-DB913140FBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1438,16 +1438,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="46.85546875" style="1" customWidth="1"/>
-    <col min="3" max="5" width="15.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="8.83203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="46.83203125" style="1" customWidth="1"/>
+    <col min="3" max="5" width="15.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1464,7 +1464,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1475,13 +1475,13 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>2818</v>
+        <v>2895</v>
       </c>
       <c r="E2" s="5">
-        <v>23.61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>52.45</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -1509,13 +1509,13 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>633</v>
+        <v>724</v>
       </c>
       <c r="E4" s="5">
-        <v>85.2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>87.53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -1526,13 +1526,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="E5" s="5">
-        <v>113.54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>113.58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -1543,13 +1543,13 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>575</v>
+        <v>677</v>
       </c>
       <c r="E6" s="5">
-        <v>90.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>91.77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -1560,13 +1560,13 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <v>1438</v>
+        <v>1502</v>
       </c>
       <c r="E7" s="5">
-        <v>22.35</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22.39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -1577,13 +1577,13 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>1784</v>
+        <v>1846</v>
       </c>
       <c r="E8" s="5">
-        <v>28.17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>28.26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -1594,13 +1594,13 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>2167</v>
+        <v>2239</v>
       </c>
       <c r="E9" s="5">
-        <v>27.58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>27.67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -1611,13 +1611,13 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>545</v>
+        <v>570</v>
       </c>
       <c r="E10" s="5">
-        <v>56.51</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>56.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>11</v>
       </c>
@@ -1628,13 +1628,13 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="E11" s="5">
-        <v>144.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>146.16999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>12</v>
       </c>
@@ -1645,13 +1645,13 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <v>604</v>
+        <v>620</v>
       </c>
       <c r="E12" s="5">
-        <v>87.34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>87.53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>13</v>
       </c>
@@ -1662,13 +1662,13 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>1678</v>
+        <v>1742</v>
       </c>
       <c r="E13" s="5">
-        <v>36.75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>14</v>
       </c>
@@ -1679,13 +1679,13 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>338</v>
+        <v>375</v>
       </c>
       <c r="E14" s="5">
-        <v>138.19999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>140.31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>15</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>55.06</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>16</v>
       </c>
@@ -1713,13 +1713,13 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>3481</v>
+        <v>4280</v>
       </c>
       <c r="E16" s="5">
-        <v>10.25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10.87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>17</v>
       </c>
@@ -1730,13 +1730,13 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>2647</v>
+        <v>2868</v>
       </c>
       <c r="E17" s="5">
-        <v>20.57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>20.75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>18</v>
       </c>
@@ -1747,13 +1747,13 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>2407</v>
+        <v>2627</v>
       </c>
       <c r="E18" s="5">
-        <v>28.14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>28.51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>19</v>
       </c>
@@ -1764,13 +1764,13 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>554</v>
+        <v>680</v>
       </c>
       <c r="E19" s="5">
-        <v>79.010000000000005</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>82.66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>20</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>184.52</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>21</v>
       </c>
@@ -1798,13 +1798,13 @@
         <v>43</v>
       </c>
       <c r="D21" s="5">
-        <v>2070</v>
+        <v>2134</v>
       </c>
       <c r="E21" s="5">
-        <v>22.29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>22.31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>22</v>
       </c>
@@ -1815,13 +1815,13 @@
         <v>45</v>
       </c>
       <c r="D22" s="5">
-        <v>449</v>
+        <v>465</v>
       </c>
       <c r="E22" s="5">
-        <v>84.88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>84.58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>23</v>
       </c>
@@ -1832,13 +1832,13 @@
         <v>47</v>
       </c>
       <c r="D23" s="5">
-        <v>2171</v>
+        <v>2474</v>
       </c>
       <c r="E23" s="5">
-        <v>15.84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15.97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>24</v>
       </c>
@@ -1849,13 +1849,13 @@
         <v>49</v>
       </c>
       <c r="D24" s="5">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E24" s="5">
-        <v>264.75</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>264.74</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>25</v>
       </c>
@@ -1866,13 +1866,13 @@
         <v>51</v>
       </c>
       <c r="D25" s="5">
-        <v>4082</v>
+        <v>4217</v>
       </c>
       <c r="E25" s="5">
-        <v>11.03</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11.04</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
         <v>26</v>
       </c>
@@ -1883,13 +1883,13 @@
         <v>53</v>
       </c>
       <c r="D26" s="5">
-        <v>907</v>
+        <v>983</v>
       </c>
       <c r="E26" s="5">
-        <v>69.48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70.44</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
         <v>27</v>
       </c>
@@ -1900,13 +1900,13 @@
         <v>55</v>
       </c>
       <c r="D27" s="5">
-        <v>2352</v>
+        <v>2507</v>
       </c>
       <c r="E27" s="5">
-        <v>26.04</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26.06</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
         <v>28</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>878.52</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>30</v>
       </c>
@@ -1934,13 +1934,13 @@
         <v>59</v>
       </c>
       <c r="D29" s="5">
-        <v>592</v>
+        <v>608</v>
       </c>
       <c r="E29" s="5">
-        <v>85.87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>85.75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>31</v>
       </c>
@@ -1951,13 +1951,13 @@
         <v>60</v>
       </c>
       <c r="D30" s="5">
-        <v>551</v>
+        <v>918</v>
       </c>
       <c r="E30" s="5">
-        <v>10.28</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>11.05</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
         <v>32</v>
       </c>
@@ -1968,13 +1968,13 @@
         <v>61</v>
       </c>
       <c r="D31" s="5">
-        <v>208</v>
+        <v>355</v>
       </c>
       <c r="E31" s="5">
-        <v>27.96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>28.41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
         <v>33</v>
       </c>
@@ -1985,13 +1985,13 @@
         <v>64</v>
       </c>
       <c r="D32" s="5">
-        <v>222</v>
+        <v>291</v>
       </c>
       <c r="E32" s="5">
-        <v>104.77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>111.35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
         <v>34</v>
       </c>
@@ -2002,10 +2002,10 @@
         <v>65</v>
       </c>
       <c r="D33" s="5">
-        <v>137</v>
+        <v>159</v>
       </c>
       <c r="E33" s="5">
-        <v>139.36000000000001</v>
+        <v>155.79</v>
       </c>
     </row>
   </sheetData>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2CFAD4-C68E-6F45-8C4C-DB913140FBDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E398FDE6-648C-DF4A-BF6B-1F7A525DE675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Manthan" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -24,6 +24,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1475,10 +1477,10 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>2895</v>
+        <v>3328</v>
       </c>
       <c r="E2" s="5">
-        <v>23.7</v>
+        <v>24.26</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1509,10 +1511,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>724</v>
+        <v>807</v>
       </c>
       <c r="E4" s="5">
-        <v>87.53</v>
+        <v>88.79</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1526,10 +1528,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="E5" s="5">
-        <v>113.58</v>
+        <v>113.94</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1543,10 +1545,10 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>677</v>
+        <v>749</v>
       </c>
       <c r="E6" s="5">
-        <v>91.77</v>
+        <v>92.27</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1560,10 +1562,10 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <v>1502</v>
+        <v>1690</v>
       </c>
       <c r="E7" s="5">
-        <v>22.39</v>
+        <v>22.52</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1577,10 +1579,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>1846</v>
+        <v>2247</v>
       </c>
       <c r="E8" s="5">
-        <v>28.26</v>
+        <v>28.83</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1594,10 +1596,10 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>2239</v>
+        <v>2438</v>
       </c>
       <c r="E9" s="5">
-        <v>27.67</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1611,15 +1613,15 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>570</v>
+        <v>651</v>
       </c>
       <c r="E10" s="5">
-        <v>56.3</v>
+        <v>55.86</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>23</v>
@@ -1628,15 +1630,15 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>268</v>
+        <v>372</v>
       </c>
       <c r="E11" s="5">
-        <v>146.16999999999999</v>
+        <v>151.35</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>25</v>
@@ -1645,15 +1647,15 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <v>620</v>
+        <v>674</v>
       </c>
       <c r="E12" s="5">
-        <v>87.53</v>
+        <v>88.12</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>27</v>
@@ -1662,15 +1664,15 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>1742</v>
+        <v>1827</v>
       </c>
       <c r="E13" s="5">
-        <v>36.6</v>
+        <v>36.36</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>29</v>
@@ -1679,15 +1681,15 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>375</v>
+        <v>431</v>
       </c>
       <c r="E14" s="5">
-        <v>140.31</v>
+        <v>142.85</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>31</v>
@@ -1704,7 +1706,7 @@
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>33</v>
@@ -1713,15 +1715,15 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>4280</v>
+        <v>4961</v>
       </c>
       <c r="E16" s="5">
-        <v>10.87</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>35</v>
@@ -1730,15 +1732,15 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>2868</v>
+        <v>3069</v>
       </c>
       <c r="E17" s="5">
-        <v>20.75</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>37</v>
@@ -1747,15 +1749,15 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>2627</v>
+        <v>2985</v>
       </c>
       <c r="E18" s="5">
-        <v>28.51</v>
+        <v>29.04</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>39</v>
@@ -1764,15 +1766,15 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>680</v>
+        <v>773</v>
       </c>
       <c r="E19" s="5">
-        <v>82.66</v>
+        <v>84.77</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>68</v>
@@ -1781,15 +1783,15 @@
         <v>41</v>
       </c>
       <c r="D20" s="5">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="E20" s="5">
-        <v>184.52</v>
+        <v>191.16</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>42</v>
@@ -1798,15 +1800,15 @@
         <v>43</v>
       </c>
       <c r="D21" s="5">
-        <v>2134</v>
+        <v>2274</v>
       </c>
       <c r="E21" s="5">
-        <v>22.31</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>44</v>
@@ -1815,15 +1817,15 @@
         <v>45</v>
       </c>
       <c r="D22" s="5">
-        <v>465</v>
+        <v>498</v>
       </c>
       <c r="E22" s="5">
-        <v>84.58</v>
+        <v>84.62</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>46</v>
@@ -1832,15 +1834,15 @@
         <v>47</v>
       </c>
       <c r="D23" s="5">
-        <v>2474</v>
+        <v>2819</v>
       </c>
       <c r="E23" s="5">
-        <v>15.97</v>
+        <v>16.149999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>48</v>
@@ -1849,15 +1851,15 @@
         <v>49</v>
       </c>
       <c r="D24" s="5">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="E24" s="5">
-        <v>264.74</v>
+        <v>265.08</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>50</v>
@@ -1866,15 +1868,15 @@
         <v>51</v>
       </c>
       <c r="D25" s="5">
-        <v>4217</v>
+        <v>4476</v>
       </c>
       <c r="E25" s="5">
-        <v>11.04</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>52</v>
@@ -1883,15 +1885,15 @@
         <v>53</v>
       </c>
       <c r="D26" s="5">
-        <v>983</v>
+        <v>1046</v>
       </c>
       <c r="E26" s="5">
-        <v>70.44</v>
+        <v>71.290000000000006</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>54</v>
@@ -1900,15 +1902,15 @@
         <v>55</v>
       </c>
       <c r="D27" s="5">
-        <v>2507</v>
+        <v>2746</v>
       </c>
       <c r="E27" s="5">
-        <v>26.06</v>
+        <v>26.18</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>56</v>
@@ -1925,7 +1927,7 @@
     </row>
     <row r="29" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>58</v>
@@ -1934,15 +1936,15 @@
         <v>59</v>
       </c>
       <c r="D29" s="5">
-        <v>608</v>
+        <v>656</v>
       </c>
       <c r="E29" s="5">
-        <v>85.75</v>
+        <v>85.54</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>62</v>
@@ -1951,15 +1953,15 @@
         <v>60</v>
       </c>
       <c r="D30" s="5">
-        <v>918</v>
+        <v>1303</v>
       </c>
       <c r="E30" s="5">
-        <v>11.05</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>63</v>
@@ -1968,15 +1970,15 @@
         <v>61</v>
       </c>
       <c r="D31" s="5">
-        <v>355</v>
+        <v>565</v>
       </c>
       <c r="E31" s="5">
-        <v>28.41</v>
+        <v>28.97</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>66</v>
@@ -1985,15 +1987,15 @@
         <v>64</v>
       </c>
       <c r="D32" s="5">
-        <v>291</v>
+        <v>331</v>
       </c>
       <c r="E32" s="5">
-        <v>111.35</v>
+        <v>112.67</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>67</v>
@@ -2002,10 +2004,10 @@
         <v>65</v>
       </c>
       <c r="D33" s="5">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E33" s="5">
-        <v>155.79</v>
+        <v>160.34</v>
       </c>
     </row>
   </sheetData>

--- a/Summary Report.xlsx
+++ b/Summary Report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manthan/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E398FDE6-648C-DF4A-BF6B-1F7A525DE675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C22838C-CF3A-EB4A-B204-99D11289CA9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1477,10 +1477,10 @@
         <v>6</v>
       </c>
       <c r="D2" s="5">
-        <v>3328</v>
+        <v>3458</v>
       </c>
       <c r="E2" s="5">
-        <v>24.26</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1511,10 +1511,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="5">
-        <v>807</v>
+        <v>886</v>
       </c>
       <c r="E4" s="5">
-        <v>88.79</v>
+        <v>89.93</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1528,10 +1528,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="5">
-        <v>443</v>
+        <v>486</v>
       </c>
       <c r="E5" s="5">
-        <v>113.94</v>
+        <v>114.9</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1545,10 +1545,10 @@
         <v>14</v>
       </c>
       <c r="D6" s="5">
-        <v>749</v>
+        <v>807</v>
       </c>
       <c r="E6" s="5">
-        <v>92.27</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1562,10 +1562,10 @@
         <v>16</v>
       </c>
       <c r="D7" s="5">
-        <v>1690</v>
+        <v>1881</v>
       </c>
       <c r="E7" s="5">
-        <v>22.52</v>
+        <v>22.65</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1579,10 +1579,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="5">
-        <v>2247</v>
+        <v>2441</v>
       </c>
       <c r="E8" s="5">
-        <v>28.83</v>
+        <v>29.29</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1596,10 +1596,10 @@
         <v>20</v>
       </c>
       <c r="D9" s="5">
-        <v>2438</v>
+        <v>2643</v>
       </c>
       <c r="E9" s="5">
-        <v>28</v>
+        <v>28.39</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1613,10 +1613,10 @@
         <v>22</v>
       </c>
       <c r="D10" s="5">
-        <v>651</v>
+        <v>750</v>
       </c>
       <c r="E10" s="5">
-        <v>55.86</v>
+        <v>55.14</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1630,10 +1630,10 @@
         <v>24</v>
       </c>
       <c r="D11" s="5">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E11" s="5">
-        <v>151.35</v>
+        <v>152.09</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1647,10 +1647,10 @@
         <v>26</v>
       </c>
       <c r="D12" s="5">
-        <v>674</v>
+        <v>729</v>
       </c>
       <c r="E12" s="5">
-        <v>88.12</v>
+        <v>88.76</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1664,10 +1664,10 @@
         <v>28</v>
       </c>
       <c r="D13" s="5">
-        <v>1827</v>
+        <v>1920</v>
       </c>
       <c r="E13" s="5">
-        <v>36.36</v>
+        <v>36.47</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1681,10 +1681,10 @@
         <v>30</v>
       </c>
       <c r="D14" s="5">
-        <v>431</v>
+        <v>454</v>
       </c>
       <c r="E14" s="5">
-        <v>142.85</v>
+        <v>144.53</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1715,10 +1715,10 @@
         <v>34</v>
       </c>
       <c r="D16" s="5">
-        <v>4961</v>
+        <v>5463</v>
       </c>
       <c r="E16" s="5">
-        <v>11.11</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1732,10 +1732,10 @@
         <v>36</v>
       </c>
       <c r="D17" s="5">
-        <v>3069</v>
+        <v>3325</v>
       </c>
       <c r="E17" s="5">
-        <v>20.9</v>
+        <v>21.19</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1749,10 +1749,10 @@
         <v>38</v>
       </c>
       <c r="D18" s="5">
-        <v>2985</v>
+        <v>3034</v>
       </c>
       <c r="E18" s="5">
-        <v>29.04</v>
+        <v>29.22</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1766,10 +1766,10 @@
         <v>40</v>
       </c>
       <c r="D19" s="5">
-        <v>773</v>
+        <v>819</v>
       </c>
       <c r="E19" s="5">
-        <v>84.77</v>
+        <v>86.95</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1783,10 +1783,10 @@
         <v>41</v>
       </c>
       <c r="D20" s="5">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="E20" s="5">
-        <v>191.16</v>
+        <v>194.65</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1800,10 +1800,10 @@
         <v>43</v>
       </c>
       <c r="D21" s="5">
-        <v>2274</v>
+        <v>2510</v>
       </c>
       <c r="E21" s="5">
-        <v>22.37</v>
+        <v>22.53</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1817,10 +1817,10 @@
         <v>45</v>
       </c>
       <c r="D22" s="5">
-        <v>498</v>
+        <v>556</v>
       </c>
       <c r="E22" s="5">
-        <v>84.62</v>
+        <v>85.33</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1834,10 +1834,10 @@
         <v>47</v>
       </c>
       <c r="D23" s="5">
-        <v>2819</v>
+        <v>3148</v>
       </c>
       <c r="E23" s="5">
-        <v>16.149999999999999</v>
+        <v>16.420000000000002</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1851,10 +1851,10 @@
         <v>49</v>
       </c>
       <c r="D24" s="5">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="E24" s="5">
-        <v>265.08</v>
+        <v>265.86</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1868,10 +1868,10 @@
         <v>51</v>
       </c>
       <c r="D25" s="5">
-        <v>4476</v>
+        <v>5078</v>
       </c>
       <c r="E25" s="5">
-        <v>11.05</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1885,10 +1885,10 @@
         <v>53</v>
       </c>
       <c r="D26" s="5">
-        <v>1046</v>
+        <v>1140</v>
       </c>
       <c r="E26" s="5">
-        <v>71.290000000000006</v>
+        <v>72.11</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1902,10 +1902,10 @@
         <v>55</v>
       </c>
       <c r="D27" s="5">
-        <v>2746</v>
+        <v>3052</v>
       </c>
       <c r="E27" s="5">
-        <v>26.18</v>
+        <v>26.26</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1936,10 +1936,10 @@
         <v>59</v>
       </c>
       <c r="D29" s="5">
-        <v>656</v>
+        <v>737</v>
       </c>
       <c r="E29" s="5">
-        <v>85.54</v>
+        <v>86.18</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1953,10 +1953,10 @@
         <v>60</v>
       </c>
       <c r="D30" s="5">
-        <v>1303</v>
+        <v>1681</v>
       </c>
       <c r="E30" s="5">
-        <v>11.25</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1970,10 +1970,10 @@
         <v>61</v>
       </c>
       <c r="D31" s="5">
-        <v>565</v>
+        <v>698</v>
       </c>
       <c r="E31" s="5">
-        <v>28.97</v>
+        <v>29.45</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1987,10 +1987,10 @@
         <v>64</v>
       </c>
       <c r="D32" s="5">
-        <v>331</v>
+        <v>394</v>
       </c>
       <c r="E32" s="5">
-        <v>112.67</v>
+        <v>116.56</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2004,10 +2004,10 @@
         <v>65</v>
       </c>
       <c r="D33" s="5">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="E33" s="5">
-        <v>160.34</v>
+        <v>172.77</v>
       </c>
     </row>
   </sheetData>
